--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1057,6 +1057,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129694622</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96071</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>505148</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6664580</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Basisk bergart (grönsten)</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Basic rock</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96071</v>
+        <v>96082</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96082</v>
+        <v>96083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96083</v>
+        <v>96088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96088</v>
+        <v>96092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96092</v>
+        <v>96094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96094</v>
+        <v>96104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96104</v>
+        <v>96108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96108</v>
+        <v>96111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96111</v>
+        <v>96112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>129694622</v>
       </c>
       <c r="B5" t="n">
-        <v>96112</v>
+        <v>96129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6778602</v>
+        <v>132227660</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>581</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trubbklockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Encalypta mutica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>I.Hagen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norsen, Dlr</t>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505094.4990142131</v>
+        <v>505129</v>
       </c>
       <c r="R2" t="n">
-        <v>6664492.297139523</v>
+        <v>6664591</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,27 +756,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-04-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-04-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst</t>
+          <t>Förekommer inom 1 dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,75 +775,98 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bar jord nedanför liten brant</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Ohlson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Ohlson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>52432</v>
+        <v>132228362</v>
       </c>
       <c r="B3" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>581</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Trubbklockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Encalypta mutica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>I.Hagen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norsen, Dlr</t>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505026.262398555</v>
+        <v>505126</v>
       </c>
       <c r="R3" t="n">
-        <v>6664371.576378326</v>
+        <v>6664592</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,89 +890,89 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-05-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-05-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tog bilder (bifogas)</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bar jord i sydvästvänd slänt</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124131064</v>
+        <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>96807</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>582</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Hårklockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Encalypta spathulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>Müll.Hal.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -971,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505137</v>
+        <v>505147</v>
       </c>
       <c r="R4" t="n">
-        <v>6664578</v>
+        <v>6664590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,24 +1014,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Återfynd</t>
+          <t>Förekom inom 11 dm2. Kollekt sparad.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,14 +1034,24 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Nedlagt kalkbrott</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Basisk bergart (grönsten)</t>
+          <t>Lera (&lt; 0,002 mm)</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Basic rock # Mycket stort block</t>
+          <t>Clay (&lt; 0,002 mm) # Bar jord i sydvästvänd slänt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,49 +1069,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129694622</v>
+        <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>96129</v>
+        <v>97152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>582</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hårklockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Encalypta spathulata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Müll.Hal.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norsberget, Dlr</t>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505148</v>
+        <v>505152</v>
       </c>
       <c r="R5" t="n">
-        <v>6664580</v>
+        <v>6664595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,12 +1142,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Förekom inom 2 dm2. Kollekt sparad.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,14 +1165,19 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Basisk bergart (grönsten)</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Nedlagt kalkbrott</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Basic rock</t>
+          <t>Bar jord på ett block</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,6 +1192,3007 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129694795</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97152</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>582</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hårklockmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Encalypta spathulata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Müll.Hal.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>505135</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6664587</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Förekom inom 20 dm2.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Nedlagt kalkbrott</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Lera (&lt; 0,002 mm)</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Clay (&lt; 0,002 mm) #  Bar jord i sydvästvänd slänt</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132225993</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97229</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>582</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hårklockmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Encalypta spathulata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Müll.Hal.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>505142</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6664595</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Förekommer inom 2 dm2</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bar jord intill granstubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132226930</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97229</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>582</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hårklockmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Encalypta spathulata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Müll.Hal.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>505146</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6664605</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Förekommer inom 1 dm2</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bar jord på block</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132228649</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97229</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>582</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Hårklockmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Encalypta spathulata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Müll.Hal.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>505127</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6664595</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Förekommer inom 10 dm2</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bar jord i sydvästvänd slänt, intill murkna vedrester</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130191015</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>505133</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6664595</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124131064</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97811</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>505137</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6664578</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Basisk bergart (grönsten)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Basic rock # Mycket stort block</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132225944</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97888</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>505140</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6664586</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm) # Stort block</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124131425</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>505154</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6664604</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Basisk bergart (grönsten)</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Basic rock # Klippvägg</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129726919</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>505124</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6664590</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Basisk bergart (grönsten)</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Basic rock</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129726980</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>505145</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6664597</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Basisk bergart (grönsten)</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Basic rock</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129694622</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>505148</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6664580</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Basisk bergart (grönsten)</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Basic rock</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130189264</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>505170</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6664585</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130188532</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>505194</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6664573</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1404137</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>505148</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6664594</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1339311</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>505148</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6664594</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129694667</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93300</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp agg.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>505166</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6664600</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129694706</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93300</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp agg.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>505156</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6664597</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1749447</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>505148</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6664594</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129694636</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>505166</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6664600</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Gruva</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Före detta kalkbrott</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130188803</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>505170</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6664585</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>52432</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>505026</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6664372</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2013-05-03</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2013-05-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Tog bilder (bifogas)</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132227114</v>
+      </c>
+      <c r="B27" t="n">
+        <v>107943</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norsberget, gammalt kalkbrott, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>505124</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6664594</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4955167</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>505148</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6664594</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6778602</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>505094</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6664492</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2007-04-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2007-04-13</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mikael Ohlson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mikael Ohlson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130189804</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>505158</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6664594</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5286387</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>505148</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6664594</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2011-09-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97152</v>
+        <v>97325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97152</v>
+        <v>97325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97152</v>
+        <v>97325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97229</v>
+        <v>97325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97229</v>
+        <v>97325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97229</v>
+        <v>97325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97325</v>
+        <v>97326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97325</v>
+        <v>97326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97325</v>
+        <v>97326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97325</v>
+        <v>97326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97325</v>
+        <v>97326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97325</v>
+        <v>97326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97333</v>
+        <v>97334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97333</v>
+        <v>97334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>97334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97333</v>
+        <v>97334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>97334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97333</v>
+        <v>97334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97334</v>
+        <v>97345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97334</v>
+        <v>97345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97334</v>
+        <v>97345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97334</v>
+        <v>97345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97334</v>
+        <v>97345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97334</v>
+        <v>97345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97345</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97345</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97345</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97345</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97345</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97345</v>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97359</v>
+        <v>97372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97359</v>
+        <v>97372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97359</v>
+        <v>97372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97359</v>
+        <v>97372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97359</v>
+        <v>97372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97359</v>
+        <v>97372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23094-2025 artfynd.xlsx
+++ b/artfynd/A 23094-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>124140322</v>
       </c>
       <c r="B4" t="n">
-        <v>97372</v>
+        <v>97373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>124140658</v>
       </c>
       <c r="B5" t="n">
-        <v>97372</v>
+        <v>97373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129694795</v>
       </c>
       <c r="B6" t="n">
-        <v>97372</v>
+        <v>97373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>132225993</v>
       </c>
       <c r="B7" t="n">
-        <v>97372</v>
+        <v>97373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>132226930</v>
       </c>
       <c r="B8" t="n">
-        <v>97372</v>
+        <v>97373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>132228649</v>
       </c>
       <c r="B9" t="n">
-        <v>97372</v>
+        <v>97373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
